--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FFCFA46-A29B-4C97-9380-71AB8F8C1774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC857A-C7C8-4723-A346-4870FB2E50AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>index</t>
   </si>
@@ -113,9 +113,6 @@
     <t>cons</t>
   </si>
   <si>
-    <t>eq</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
@@ -123,6 +120,30 @@
   </si>
   <si>
     <t>EnemyOrder</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Eq1</t>
+  </si>
+  <si>
+    <t>Eq2</t>
+  </si>
+  <si>
+    <t>Eq3</t>
+  </si>
+  <si>
+    <t>Eq</t>
+  </si>
+  <si>
+    <t>Map6</t>
   </si>
 </sst>
 </file>
@@ -152,7 +173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -160,12 +181,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7551D5-D024-45F6-B620-55F7C93AE9D0}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -508,467 +545,830 @@
     <col min="4" max="4" width="12.21875" customWidth="1"/>
     <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="H7" s="1">
+        <v>5</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
         <v>57</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
         <v>58</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
         <v>69</v>
       </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC857A-C7C8-4723-A346-4870FB2E50AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C18961-EA53-4D13-AC26-2651B90527A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="1824" yWindow="0" windowWidth="20208" windowHeight="12360" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>index</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Map6</t>
+  </si>
+  <si>
+    <t>Key1</t>
   </si>
 </sst>
 </file>
@@ -173,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -196,13 +199,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,8 +608,8 @@
       <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -619,7 +634,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -644,7 +659,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
@@ -667,7 +682,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1">
         <v>3</v>
@@ -690,7 +705,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1">
         <v>4</v>
@@ -712,7 +727,9 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="H7" s="1">
         <v>5</v>
       </c>

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C18961-EA53-4D13-AC26-2651B90527A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFA2CC-8869-4B60-A505-C99A069E28E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="0" windowWidth="20208" windowHeight="12360" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="1824" yWindow="1524" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>index</t>
   </si>
@@ -147,6 +147,15 @@
   </si>
   <si>
     <t>Key1</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>Companion1</t>
+  </si>
+  <si>
+    <t>Companion2</t>
   </si>
 </sst>
 </file>
@@ -214,9 +223,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -552,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7551D5-D024-45F6-B620-55F7C93AE9D0}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -560,10 +570,11 @@
     <col min="4" max="4" width="12.21875" customWidth="1"/>
     <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,17 +593,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -611,17 +625,20 @@
       <c r="F2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1">
+      <c r="G2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -636,17 +653,20 @@
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1">
+      <c r="G3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -661,17 +681,17 @@
       <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>2</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -684,17 +704,17 @@
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -707,17 +727,17 @@
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>4</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -730,13 +750,13 @@
       <c r="F7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -747,13 +767,13 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>6</v>
       </c>
-      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -765,7 +785,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -777,27 +797,31 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -807,7 +831,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -817,7 +841,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -827,7 +851,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFA2CC-8869-4B60-A505-C99A069E28E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1D56C7-C5D7-47BD-B19E-827FCED4410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="1524" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="2520" yWindow="1836" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>index</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Eq</t>
   </si>
   <si>
-    <t>Map6</t>
-  </si>
-  <si>
     <t>Key1</t>
   </si>
   <si>
@@ -156,6 +153,15 @@
   </si>
   <si>
     <t>Companion2</t>
+  </si>
+  <si>
+    <t>Exit18</t>
+  </si>
+  <si>
+    <t>Exit19</t>
+  </si>
+  <si>
+    <t>Warning</t>
   </si>
 </sst>
 </file>
@@ -223,11 +229,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,8 +598,8 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>37</v>
+      <c r="G1" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>23</v>
@@ -623,10 +628,10 @@
         <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
@@ -653,8 +658,8 @@
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>39</v>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I3" s="1">
         <v>1</v>
@@ -674,7 +679,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -698,7 +703,9 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -721,7 +728,9 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
@@ -802,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -814,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1D56C7-C5D7-47BD-B19E-827FCED4410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16275EA-CB04-4A8C-8E31-4BA49E19FF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1836" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="2520" yWindow="1596" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>index</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Warning</t>
+  </si>
+  <si>
+    <t>Boss1</t>
   </si>
 </sst>
 </file>
@@ -753,7 +756,9 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16275EA-CB04-4A8C-8E31-4BA49E19FF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42885907-DC14-497D-89B9-3D5833D60E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1596" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="5292" yWindow="3948" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -815,10 +815,9 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -827,10 +826,9 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>

--- a/Sheets/Data.xlsx
+++ b/Sheets/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nosoy\Documents\RPG Godot 4.2\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42885907-DC14-497D-89B9-3D5833D60E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8784FE72-8F32-421F-B86D-D3CDDFE64DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5292" yWindow="3948" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
+    <workbookView xWindow="744" yWindow="1200" windowWidth="20208" windowHeight="10764" xr2:uid="{5BAAA14F-01DF-476C-B593-E5F04671D68B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>index</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>Boss1</t>
+  </si>
+  <si>
+    <t>ItemNPC1</t>
+  </si>
+  <si>
+    <t>ItemNPC2</t>
   </si>
 </sst>
 </file>
@@ -232,10 +238,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,6 +696,9 @@
       <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="I4" s="1">
         <v>2</v>
       </c>
@@ -713,6 +723,9 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
